--- a/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD5B186-0DD3-47F4-95E6-E07B22F9DF18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89C90E8F-C173-4832-B1FE-655A3B6ABAAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -90,21 +90,7 @@
     <t>##</t>
   </si>
   <si>
-    <t>模值x1</t>
-  </si>
-  <si>
-    <t>描述:模值x1</t>
-  </si>
-  <si>
     <t>时间轴技能名字</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能描述</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能Task：支持多态，添加新AbilityTask类型去__bean__中添加即可。暂定给了13个变量的预留位，不够的话就自己加长。</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
@@ -156,19 +142,57 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
+    <t>轨道2</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>*abilityTask</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
     <t>TaskDoCost</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>轨道2</t>
-    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>TaskDebug</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>abilityTask</t>
+  </si>
+  <si>
+    <t>测试1</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试135</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试时间轴1</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间轴技能描述</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能Task：支持多态，添加新AbilityTask类型去__bean__中添加即可。暂定给了10个变量的预留位，不够的话就自己加长。</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试描述1</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试描述2</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试时间轴2</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>开头</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>结尾</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -246,7 +270,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -257,12 +281,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
@@ -271,6 +289,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -580,30 +613,30 @@
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="7"/>
+        <v>12</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="13"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="10"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -619,34 +652,34 @@
         <v>6</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
-      <c r="W2" s="7"/>
+        <v>13</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="13"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="10"/>
     </row>
     <row r="3" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>19</v>
+      <c r="A3" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -654,26 +687,26 @@
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="10"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -683,38 +716,38 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="F4" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="9"/>
-      <c r="W4" s="10"/>
+        <v>19</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="8"/>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -722,31 +755,31 @@
         <v>101</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="E5" s="5">
+        <v>100</v>
+      </c>
+      <c r="F5" s="5" t="b">
+        <v>0</v>
+      </c>
       <c r="G5" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I5" s="5">
         <v>1</v>
       </c>
       <c r="J5" s="4">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>1</v>
-      </c>
-      <c r="L5" s="2">
-        <v>0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="K5" s="5"/>
+      <c r="L5" s="2"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -757,20 +790,18 @@
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="5">
-        <v>1</v>
+        <v>24</v>
+      </c>
+      <c r="I6" s="4">
+        <v>2</v>
       </c>
       <c r="J6" s="4">
-        <v>0</v>
-      </c>
-      <c r="K6" s="5">
-        <v>1</v>
-      </c>
-      <c r="L6" s="4">
-        <v>0</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="4"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B7" s="3"/>
@@ -779,23 +810,19 @@
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I7" s="5">
         <v>1</v>
       </c>
       <c r="J7" s="4">
-        <v>0</v>
-      </c>
-      <c r="K7" s="5">
         <v>1</v>
       </c>
-      <c r="L7" s="4">
-        <v>0</v>
-      </c>
+      <c r="K7" s="5"/>
+      <c r="L7" s="4"/>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B8" s="5"/>
@@ -805,30 +832,50 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8" s="5">
-        <v>1</v>
+        <v>24</v>
+      </c>
+      <c r="I8" s="4">
+        <v>5</v>
       </c>
       <c r="J8" s="4">
+        <v>6</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" s="4"/>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B9" s="5">
+        <v>102</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="5">
+        <v>50</v>
+      </c>
+      <c r="F9" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="K8" s="5">
-        <v>1</v>
-      </c>
-      <c r="L8" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B9" s="1"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
+      <c r="G9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="5">
+        <v>3</v>
+      </c>
+      <c r="J9" s="4">
+        <v>4</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B10" s="1"/>
@@ -837,8 +884,18 @@
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
+      <c r="H10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="5">
+        <v>15</v>
+      </c>
+      <c r="J10" s="4">
+        <v>50</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C11" s="5"/>
@@ -971,10 +1028,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="H4:W4"/>
-    <mergeCell ref="H3:W3"/>
-    <mergeCell ref="G2:W2"/>
-    <mergeCell ref="G1:W1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="H3:Q3"/>
+    <mergeCell ref="H4:Q4"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89C90E8F-C173-4832-B1FE-655A3B6ABAAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5535105-2375-4BB9-AA29-66151DBA96E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
   <si>
     <t>##var</t>
   </si>
@@ -73,9 +73,6 @@
   </si>
   <si>
     <t>name</t>
-  </si>
-  <si>
-    <t>desc</t>
   </si>
   <si>
     <t>##type</t>
@@ -168,19 +165,7 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>时间轴技能描述</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>技能Task：支持多态，添加新AbilityTask类型去__bean__中添加即可。暂定给了10个变量的预留位，不够的话就自己加长。</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试描述1</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试描述2</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
@@ -296,14 +281,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -586,20 +571,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W27"/>
+  <dimension ref="A1:V27"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="16.21875" style="4" customWidth="1"/>
-    <col min="4" max="5" width="14.44140625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="20.5546875" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.44140625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="18.109375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="14.44140625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="16.77734375" style="4" customWidth="1"/>
-    <col min="11" max="11" width="15" style="4" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="20.5546875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="18.109375" style="4" customWidth="1"/>
+    <col min="8" max="8" width="14.44140625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="16.77734375" style="4" customWidth="1"/>
+    <col min="10" max="10" width="15" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -609,19 +594,17 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
+      <c r="D1" s="5" t="s">
+        <v>8</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" s="13"/>
+        <v>11</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="11"/>
+      <c r="H1" s="9"/>
       <c r="I1" s="9"/>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
@@ -635,32 +618,29 @@
       <c r="S1" s="9"/>
       <c r="T1" s="9"/>
       <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="10"/>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="V1" s="10"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
+      <c r="D2" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="13"/>
+        <v>12</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="11"/>
+      <c r="H2" s="9"/>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
@@ -674,24 +654,23 @@
       <c r="S2" s="9"/>
       <c r="T2" s="9"/>
       <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="10"/>
-    </row>
-    <row r="3" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="V2" s="10"/>
+    </row>
+    <row r="3" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>22</v>
-      </c>
+      <c r="F3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="12"/>
       <c r="I3" s="12"/>
       <c r="J3" s="12"/>
       <c r="K3" s="12"/>
@@ -700,231 +679,214 @@
       <c r="N3" s="12"/>
       <c r="O3" s="12"/>
       <c r="P3" s="12"/>
-      <c r="Q3" s="12"/>
+      <c r="Q3" s="9"/>
       <c r="R3" s="9"/>
       <c r="S3" s="9"/>
       <c r="T3" s="9"/>
       <c r="U3" s="9"/>
-      <c r="V3" s="9"/>
-      <c r="W3" s="10"/>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="V3" s="10"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>28</v>
+        <v>7</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
+        <v>18</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
       <c r="T4" s="7"/>
       <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="8"/>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="V4" s="8"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>101</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="5">
+        <v>26</v>
+      </c>
+      <c r="D5" s="5">
         <v>100</v>
       </c>
-      <c r="F5" s="5" t="b">
+      <c r="E5" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="F5" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="G5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="5">
+        <v>22</v>
+      </c>
+      <c r="H5" s="5">
         <v>1</v>
       </c>
-      <c r="J5" s="4">
+      <c r="I5" s="4">
         <v>3</v>
       </c>
-      <c r="K5" s="5"/>
-      <c r="L5" s="2"/>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="J5" s="5"/>
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5" t="s">
+      <c r="G6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="4">
+        <v>2</v>
+      </c>
+      <c r="I6" s="4">
+        <v>4</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="4">
-        <v>2</v>
-      </c>
-      <c r="J6" s="4">
-        <v>4</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6" s="4"/>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="K6" s="4"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B7" s="3"/>
       <c r="C7" s="1"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="F7" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="G7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="5">
+        <v>22</v>
+      </c>
+      <c r="H7" s="5">
         <v>1</v>
       </c>
-      <c r="J7" s="4">
+      <c r="I7" s="4">
         <v>1</v>
       </c>
-      <c r="K7" s="5"/>
-      <c r="L7" s="4"/>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="J7" s="5"/>
+      <c r="K7" s="4"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5" t="s">
-        <v>24</v>
+      <c r="G8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="4">
+        <v>5</v>
       </c>
       <c r="I8" s="4">
-        <v>5</v>
-      </c>
-      <c r="J8" s="4">
         <v>6</v>
       </c>
-      <c r="K8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L8" s="4"/>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="J8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="4"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <v>102</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="5">
+        <v>28</v>
+      </c>
+      <c r="D9" s="5">
         <v>50</v>
       </c>
-      <c r="F9" s="5" t="b">
+      <c r="E9" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="F9" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="G9" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9" s="5">
+        <v>23</v>
+      </c>
+      <c r="H9" s="5">
         <v>3</v>
       </c>
-      <c r="J9" s="4">
+      <c r="I9" s="4">
         <v>4</v>
       </c>
-      <c r="K9" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="J9" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B10" s="1"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" s="5">
+      <c r="G10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="5">
         <v>15</v>
       </c>
-      <c r="J10" s="4">
+      <c r="I10" s="4">
         <v>50</v>
       </c>
-      <c r="K10" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="J10" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -932,9 +894,8 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -942,9 +903,8 @@
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -952,9 +912,8 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
@@ -962,9 +921,8 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="1"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -972,9 +930,8 @@
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="1"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
@@ -982,9 +939,8 @@
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
@@ -992,9 +948,8 @@
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="1"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
@@ -1002,9 +957,8 @@
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
@@ -1012,26 +966,25 @@
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="1"/>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="1"/>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="5"/>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="H3:Q3"/>
-    <mergeCell ref="H4:Q4"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="G3:P3"/>
+    <mergeCell ref="G4:P4"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5535105-2375-4BB9-AA29-66151DBA96E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2518EBD-28CC-404F-8C56-BF75D714946C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REPO\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2518EBD-28CC-404F-8C56-BF75D714946C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,12 +27,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>fangmenglu</author>
   </authors>
   <commentList>
-    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="C5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -64,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -72,9 +71,6 @@
     <t>id</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -91,19 +87,11 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>lifeTime</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>技能生命时长</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>manualEndAbility</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
@@ -119,18 +107,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>name</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>*tracks</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>array,track</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>轨道名</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -143,10 +119,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>*abilityTask</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>TaskDoCost</t>
   </si>
   <si>
@@ -178,13 +150,117 @@
   </si>
   <si>
     <t>结尾</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>array,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rack</t>
+    </r>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>*TaskClips</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>StartTime</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>EndTime</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Task</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>结束帧</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>开始帧</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>racks</t>
+    </r>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>ManualEndAbility</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>LifeTime</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -255,7 +331,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -282,18 +358,24 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -570,40 +652,40 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V27"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:X28"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="16.21875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="20.5546875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="14.44140625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="18.109375" style="4" customWidth="1"/>
-    <col min="8" max="8" width="14.44140625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16.77734375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="16.25" style="4" customWidth="1"/>
+    <col min="4" max="4" width="14.5" style="4" customWidth="1"/>
+    <col min="5" max="5" width="20.5" style="4" customWidth="1"/>
+    <col min="6" max="6" width="14.5" style="4" customWidth="1"/>
+    <col min="7" max="7" width="18.125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="14.5" style="4" customWidth="1"/>
+    <col min="9" max="9" width="16.75" style="4" customWidth="1"/>
     <col min="10" max="10" width="15" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="11"/>
+      <c r="B1" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="12"/>
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
       <c r="J1" s="9"/>
@@ -620,26 +702,26 @@
       <c r="U1" s="9"/>
       <c r="V1" s="10"/>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="D2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="11"/>
+      <c r="F2" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="12"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
@@ -656,60 +738,55 @@
       <c r="U2" s="9"/>
       <c r="V2" s="10"/>
     </row>
-    <row r="3" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
-      <c r="F3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>21</v>
+      <c r="F3" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>26</v>
       </c>
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
-      <c r="O3" s="12"/>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
-      <c r="V3" s="10"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="13" t="s">
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="11"/>
+      <c r="R3" s="11"/>
+      <c r="S3" s="11"/>
+      <c r="T3" s="11"/>
+      <c r="U3" s="11"/>
+      <c r="V3" s="11"/>
+      <c r="W3" s="11"/>
+      <c r="X3" s="10"/>
+    </row>
+    <row r="4" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="G4" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
+      <c r="H4" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>29</v>
+      </c>
       <c r="J4" s="13"/>
       <c r="K4" s="13"/>
       <c r="L4" s="13"/>
@@ -717,168 +794,208 @@
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
       <c r="P4" s="13"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="8"/>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1">
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="13"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="10"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="8"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1">
         <v>101</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="5">
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="5">
         <v>100</v>
       </c>
-      <c r="E5" s="5" t="b">
+      <c r="E6" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="5">
+      <c r="F6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="5">
         <v>1</v>
       </c>
-      <c r="I5" s="4">
+      <c r="H6" s="4">
         <v>3</v>
       </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="2"/>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="4">
-        <v>2</v>
-      </c>
-      <c r="I6" s="4">
-        <v>4</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="K6" s="4"/>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B7" s="3"/>
-      <c r="C7" s="1"/>
+      <c r="I6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="L6" s="5"/>
+      <c r="M6" s="2"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
-      <c r="F7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="5">
-        <v>1</v>
-      </c>
-      <c r="I7" s="4">
-        <v>1</v>
-      </c>
-      <c r="J7" s="5"/>
-      <c r="K7" s="4"/>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="4">
+        <v>2</v>
+      </c>
+      <c r="H7" s="4">
+        <v>4</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="M7" s="4"/>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B8" s="3"/>
+      <c r="C8" s="1"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5" t="s">
-        <v>23</v>
+      <c r="F8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="5">
+        <v>1</v>
       </c>
       <c r="H8" s="4">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="5"/>
+      <c r="M8" s="4"/>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="4">
         <v>5</v>
       </c>
-      <c r="I8" s="4">
+      <c r="H9" s="4">
         <v>6</v>
       </c>
-      <c r="J8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="K8" s="4"/>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B9" s="5">
+      <c r="I9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" s="4"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B10" s="5">
         <v>102</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="5">
         <v>50</v>
       </c>
-      <c r="E9" s="5" t="b">
+      <c r="E10" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="5">
+      <c r="F10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="5">
         <v>3</v>
       </c>
-      <c r="I9" s="4">
+      <c r="H10" s="4">
         <v>4</v>
       </c>
-      <c r="J9" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B10" s="1"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="5">
-        <v>15</v>
-      </c>
-      <c r="I10" s="4">
-        <v>50</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="I10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B11" s="1"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="G11" s="5">
+        <v>15</v>
+      </c>
+      <c r="H11" s="4">
+        <v>50</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="I12" s="5"/>
+      <c r="K12" s="4"/>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -886,8 +1003,7 @@
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B14" s="5"/>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
@@ -895,8 +1011,8 @@
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B15" s="1"/>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
@@ -904,7 +1020,7 @@
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B16" s="1"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -913,7 +1029,7 @@
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17" s="1"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
@@ -922,7 +1038,7 @@
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" s="1"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -931,7 +1047,7 @@
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="1"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
@@ -940,7 +1056,7 @@
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" s="1"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
@@ -949,7 +1065,7 @@
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="1"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
@@ -958,8 +1074,8 @@
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="5"/>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B22" s="1"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
@@ -967,28 +1083,38 @@
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="1"/>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" s="1"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="5"/>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="1"/>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B25" s="1"/>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B27" s="5"/>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B28" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="F2:G2"/>
-    <mergeCell ref="G3:P3"/>
-    <mergeCell ref="G4:P4"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="I4:S4"/>
+    <mergeCell ref="I5:S5"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
   <si>
     <t>##var</t>
   </si>
@@ -183,10 +183,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>*TaskClips</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>StartTime</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -204,6 +200,34 @@
   </si>
   <si>
     <t>开始帧</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>LifeTime</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>ManualEndAbility</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
@@ -233,27 +257,7 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>ManualEndAbility</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>LifeTime</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>I</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
+    <t>*TaskClips</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -360,17 +364,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -670,22 +674,22 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="12"/>
+      <c r="G1" s="14"/>
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
       <c r="J1" s="9"/>
@@ -718,10 +722,10 @@
       <c r="E2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="12"/>
+      <c r="G2" s="14"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
@@ -746,14 +750,14 @@
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
+      <c r="G3" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
       <c r="L3" s="11"/>
@@ -778,25 +782,25 @@
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="I4" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
-      <c r="S4" s="13"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="15"/>
       <c r="T4" s="9"/>
       <c r="U4" s="9"/>
       <c r="V4" s="9"/>
@@ -822,25 +826,25 @@
       <c r="F5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" s="15" t="s">
+      <c r="G5" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="H5" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="13"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
+      <c r="S5" s="15"/>
       <c r="T5" s="7"/>
       <c r="U5" s="7"/>
       <c r="V5" s="7"/>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REPO\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A63F5F8-FF74-4F3C-8A44-64765C546AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,12 +28,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>fangmenglu</author>
   </authors>
   <commentList>
-    <comment ref="C5" authorId="0" shapeId="0">
+    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -63,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="43">
   <si>
     <t>##var</t>
   </si>
@@ -260,11 +261,35 @@
     <t>*TaskClips</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
+  <si>
+    <t>任务名（编辑时展示用）</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗，产生CD</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>调试1</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>调试2</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>调试3</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>调试5</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -379,7 +404,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -656,21 +681,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X28"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Y28"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="16.25" style="4" customWidth="1"/>
-    <col min="4" max="4" width="14.5" style="4" customWidth="1"/>
-    <col min="5" max="5" width="20.5" style="4" customWidth="1"/>
-    <col min="6" max="6" width="14.5" style="4" customWidth="1"/>
-    <col min="7" max="7" width="18.125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="14.5" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16.75" style="4" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="18.109375" style="4" customWidth="1"/>
+    <col min="8" max="8" width="14.44140625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="16.77734375" style="4" customWidth="1"/>
     <col min="10" max="10" width="15" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -706,7 +731,7 @@
       <c r="U1" s="9"/>
       <c r="V1" s="10"/>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -742,7 +767,7 @@
       <c r="U2" s="9"/>
       <c r="V2" s="10"/>
     </row>
-    <row r="3" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>11</v>
       </c>
@@ -774,7 +799,7 @@
       <c r="W3" s="11"/>
       <c r="X3" s="10"/>
     </row>
-    <row r="4" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>11</v>
       </c>
@@ -788,10 +813,12 @@
       <c r="H4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="15"/>
       <c r="K4" s="15"/>
       <c r="L4" s="15"/>
       <c r="M4" s="15"/>
@@ -801,13 +828,14 @@
       <c r="Q4" s="15"/>
       <c r="R4" s="15"/>
       <c r="S4" s="15"/>
-      <c r="T4" s="9"/>
+      <c r="T4" s="15"/>
       <c r="U4" s="9"/>
       <c r="V4" s="9"/>
       <c r="W4" s="9"/>
-      <c r="X4" s="10"/>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="X4" s="9"/>
+      <c r="Y4" s="10"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -832,10 +860,12 @@
       <c r="H5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="15"/>
       <c r="K5" s="15"/>
       <c r="L5" s="15"/>
       <c r="M5" s="15"/>
@@ -845,13 +875,14 @@
       <c r="Q5" s="15"/>
       <c r="R5" s="15"/>
       <c r="S5" s="15"/>
-      <c r="T5" s="7"/>
+      <c r="T5" s="15"/>
       <c r="U5" s="7"/>
       <c r="V5" s="7"/>
       <c r="W5" s="7"/>
-      <c r="X5" s="8"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="X5" s="7"/>
+      <c r="Y5" s="8"/>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>101</v>
@@ -874,13 +905,17 @@
       <c r="H6" s="4">
         <v>3</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="5"/>
-      <c r="M6" s="2"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="K6" s="4"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="2"/>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="5"/>
@@ -893,15 +928,18 @@
       <c r="H7" s="4">
         <v>4</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="K7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M7" s="4"/>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="N7" s="4"/>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B8" s="3"/>
       <c r="C8" s="1"/>
       <c r="D8" s="5"/>
@@ -915,13 +953,16 @@
       <c r="H8" s="4">
         <v>1</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="5"/>
-      <c r="M8" s="4"/>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="K8" s="5"/>
+      <c r="N8" s="4"/>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -933,15 +974,18 @@
       <c r="H9" s="4">
         <v>6</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="K9" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="M9" s="4"/>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="N9" s="4"/>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B10" s="5">
         <v>102</v>
       </c>
@@ -963,14 +1007,17 @@
       <c r="H10" s="4">
         <v>4</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="K10" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B11" s="1"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -982,14 +1029,17 @@
       <c r="H11" s="4">
         <v>50</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="K11" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
@@ -999,7 +1049,7 @@
       <c r="I12" s="5"/>
       <c r="K12" s="4"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -1007,7 +1057,7 @@
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
@@ -1015,7 +1065,7 @@
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -1024,7 +1074,7 @@
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -1033,7 +1083,7 @@
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
@@ -1042,7 +1092,7 @@
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="1"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -1051,7 +1101,7 @@
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="1"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
@@ -1060,7 +1110,7 @@
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
@@ -1069,7 +1119,7 @@
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="1"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
@@ -1078,7 +1128,7 @@
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="1"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
@@ -1087,7 +1137,7 @@
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
@@ -1096,16 +1146,16 @@
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="1"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="1"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="5"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="1"/>
     </row>
   </sheetData>
@@ -1113,8 +1163,8 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="G3:I3"/>
-    <mergeCell ref="I4:S4"/>
-    <mergeCell ref="I5:S5"/>
+    <mergeCell ref="J4:T4"/>
+    <mergeCell ref="J5:T5"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A63F5F8-FF74-4F3C-8A44-64765C546AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE8EABE-EFB7-4E34-9C2F-BACCF814F868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -360,7 +360,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -393,9 +393,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -714,10 +711,10 @@
       <c r="F1" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="14"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
       <c r="K1" s="9"/>
       <c r="L1" s="9"/>
       <c r="M1" s="9"/>
@@ -750,10 +747,10 @@
       <c r="F2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="14"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
       <c r="M2" s="9"/>
@@ -781,9 +778,9 @@
       <c r="G3" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="11"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
       <c r="K3" s="11"/>
       <c r="L3" s="11"/>
       <c r="M3" s="11"/>
@@ -816,19 +813,19 @@
       <c r="I4" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="15" t="s">
+      <c r="J4" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="15"/>
-      <c r="S4" s="15"/>
-      <c r="T4" s="15"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
       <c r="U4" s="9"/>
       <c r="V4" s="9"/>
       <c r="W4" s="9"/>
@@ -863,19 +860,19 @@
       <c r="I5" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="15"/>
-      <c r="S5" s="15"/>
-      <c r="T5" s="15"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
+      <c r="T5" s="14"/>
       <c r="U5" s="7"/>
       <c r="V5" s="7"/>
       <c r="W5" s="7"/>
@@ -1160,11 +1157,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="G3:I3"/>
     <mergeCell ref="J4:T4"/>
     <mergeCell ref="J5:T5"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="F1:J1"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
@@ -218,7 +218,7 @@
     <t>TaskDebug</t>
   </si>
   <si>
-    <t>测试1</t>
+    <t>测试：输出666</t>
   </si>
   <si>
     <t>轨道2</t>
@@ -824,7 +824,7 @@
         <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="E6" s="3" t="b">
         <v>0</v>
@@ -847,10 +847,10 @@
     </row>
     <row r="7">
       <c r="G7" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H7" s="3">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>29</v>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
@@ -212,13 +212,13 @@
     <t>TaskDoCost</t>
   </si>
   <si>
-    <t>调试123</t>
+    <t>调试1235</t>
   </si>
   <si>
     <t>TaskDebug</t>
   </si>
   <si>
-    <t>测试：输出666</t>
+    <t>阿斯顿路</t>
   </si>
   <si>
     <t>轨道2</t>
@@ -867,10 +867,10 @@
         <v>32</v>
       </c>
       <c r="G8" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H8" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>27</v>
@@ -884,7 +884,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>33</v>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>##var</t>
   </si>
@@ -219,6 +219,15 @@
   </si>
   <si>
     <t>阿斯顿路</t>
+  </si>
+  <si>
+    <t>播放Cue2</t>
+  </si>
+  <si>
+    <t>TaskPlayCue</t>
+  </si>
+  <si>
+    <t>1001;1002</t>
   </si>
   <si>
     <t>轨道2</t>
@@ -616,7 +625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y11"/>
+  <dimension ref="A1:Y12"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="16.21875" customWidth="1" style="3"/>
@@ -824,7 +833,7 @@
         <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E6" s="3" t="b">
         <v>0</v>
@@ -863,60 +872,45 @@
       </c>
     </row>
     <row r="8">
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3">
+        <v>20</v>
+      </c>
+      <c r="H8" s="3">
+        <v>41</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="3">
+      <c r="J8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="F9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="3">
         <v>25</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H9" s="3">
         <v>25</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9">
-      <c r="G9" s="3">
-        <v>5</v>
-      </c>
-      <c r="H9" s="3">
-        <v>13</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
     <row r="10">
-      <c r="B10" s="2">
-        <v>102</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="3">
-        <v>50</v>
-      </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="G10" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>36</v>
@@ -929,20 +923,52 @@
       </c>
     </row>
     <row r="11">
+      <c r="B11" s="2">
+        <v>102</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="3">
+        <v>50</v>
+      </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="G11" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H11" s="3">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>30</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="G12" s="3">
+        <v>15</v>
+      </c>
+      <c r="H12" s="3">
+        <v>50</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>##var</t>
   </si>
@@ -203,43 +203,55 @@
     <t>测试时间轴1</t>
   </si>
   <si>
+    <t>动画轨道</t>
+  </si>
+  <si>
+    <t>播放攻击动画</t>
+  </si>
+  <si>
+    <t>TaskPlayCue</t>
+  </si>
+  <si>
+    <t>0;0</t>
+  </si>
+  <si>
+    <t>音效轨道</t>
+  </si>
+  <si>
+    <t>播放攻击音效</t>
+  </si>
+  <si>
+    <t>TaskDebug</t>
+  </si>
+  <si>
+    <t>测试135</t>
+  </si>
+  <si>
+    <t>特效轨道</t>
+  </si>
+  <si>
+    <t>添加拖尾特效</t>
+  </si>
+  <si>
+    <t>TaskDoNothing</t>
+  </si>
+  <si>
+    <t>GE轨道</t>
+  </si>
+  <si>
+    <t>消耗</t>
+  </si>
+  <si>
+    <t>TaskDoCost</t>
+  </si>
+  <si>
+    <t>造成伤害</t>
+  </si>
+  <si>
+    <t>测试时间轴2</t>
+  </si>
+  <si>
     <t>轨道1</t>
-  </si>
-  <si>
-    <t>消耗，产生CD</t>
-  </si>
-  <si>
-    <t>TaskDoCost</t>
-  </si>
-  <si>
-    <t>调试1235</t>
-  </si>
-  <si>
-    <t>TaskDebug</t>
-  </si>
-  <si>
-    <t>阿斯顿路</t>
-  </si>
-  <si>
-    <t>播放Cue2</t>
-  </si>
-  <si>
-    <t>TaskPlayCue</t>
-  </si>
-  <si>
-    <t>1001;1002</t>
-  </si>
-  <si>
-    <t>轨道2</t>
-  </si>
-  <si>
-    <t>调试2</t>
-  </si>
-  <si>
-    <t>测试135</t>
-  </si>
-  <si>
-    <t>测试时间轴2</t>
   </si>
   <si>
     <t>调试3</t>
@@ -833,7 +845,7 @@
         <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="E6" s="3" t="b">
         <v>0</v>
@@ -842,10 +854,10 @@
         <v>26</v>
       </c>
       <c r="G6" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H6" s="3">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>27</v>
@@ -853,73 +865,76 @@
       <c r="J6" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="K6" s="2" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="7">
+      <c r="F7" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="G7" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H7" s="3">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8">
+      <c r="F8" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="G8" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H8" s="3">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
       <c r="F9" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G9" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H9" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
       <c r="G10" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H10" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
@@ -927,7 +942,7 @@
         <v>102</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D11" s="3">
         <v>50</v>
@@ -936,7 +951,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="G11" s="3">
         <v>3</v>
@@ -945,13 +960,13 @@
         <v>4</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
@@ -962,13 +977,13 @@
         <v>50</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
@@ -200,7 +200,7 @@
     <t>技能Task：支持多态，添加新AbilityTask类型去__bean__中添加即可。暂定给了10个变量的预留位，不够的话就自己加长。</t>
   </si>
   <si>
-    <t>测试时间轴1</t>
+    <t>普通攻击</t>
   </si>
   <si>
     <t>动画轨道</t>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE8EABE-EFB7-4E34-9C2F-BACCF814F868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46AB0371-B164-4F0E-9E69-3FFF08E9C42D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511" fullCalcOnLoad="1"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -64,15 +64,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="51">
   <si>
     <t>##var</t>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <t>I</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -82,7 +82,7 @@
       </rPr>
       <t>D</t>
     </r>
-    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>Name</t>
@@ -94,10 +94,10 @@
     <t>ManualEndAbility</t>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <t>*</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -107,7 +107,7 @@
       </rPr>
       <t>T</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -117,7 +117,7 @@
       </rPr>
       <t>racks</t>
     </r>
-    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>##type</t>
@@ -132,10 +132,10 @@
     <t>bool</t>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <t>array,</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -145,7 +145,7 @@
       </rPr>
       <t>T</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -155,7 +155,7 @@
       </rPr>
       <t>rack</t>
     </r>
-    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>*TaskClips</t>
@@ -197,9 +197,6 @@
     <t>任务名（编辑时展示用）</t>
   </si>
   <si>
-    <t>技能Task：支持多态，添加新AbilityTask类型去__bean__中添加即可。暂定给了10个变量的预留位，不够的话就自己加长。</t>
-  </si>
-  <si>
     <t>普通攻击</t>
   </si>
   <si>
@@ -209,69 +206,90 @@
     <t>播放攻击动画</t>
   </si>
   <si>
+    <t>音效轨道</t>
+  </si>
+  <si>
+    <t>播放攻击音效</t>
+  </si>
+  <si>
+    <t>TaskDebug</t>
+  </si>
+  <si>
+    <t>测试135</t>
+  </si>
+  <si>
+    <t>特效轨道</t>
+  </si>
+  <si>
+    <t>添加拖尾特效</t>
+  </si>
+  <si>
+    <t>TaskDoNothing</t>
+  </si>
+  <si>
+    <t>GE轨道</t>
+  </si>
+  <si>
+    <t>消耗</t>
+  </si>
+  <si>
+    <t>TaskDoCost</t>
+  </si>
+  <si>
+    <t>造成伤害</t>
+  </si>
+  <si>
+    <t>测试时间轴2</t>
+  </si>
+  <si>
+    <t>轨道1</t>
+  </si>
+  <si>
+    <t>调试3</t>
+  </si>
+  <si>
+    <t>开头</t>
+  </si>
+  <si>
+    <t>调试5</t>
+  </si>
+  <si>
+    <t>结尾</t>
+  </si>
+  <si>
     <t>TaskPlayCue</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>0;0</t>
-  </si>
-  <si>
-    <t>音效轨道</t>
-  </si>
-  <si>
-    <t>播放攻击音效</t>
-  </si>
-  <si>
-    <t>TaskDebug</t>
-  </si>
-  <si>
-    <t>测试135</t>
-  </si>
-  <si>
-    <t>特效轨道</t>
-  </si>
-  <si>
-    <t>添加拖尾特效</t>
-  </si>
-  <si>
-    <t>TaskDoNothing</t>
-  </si>
-  <si>
-    <t>GE轨道</t>
-  </si>
-  <si>
-    <t>消耗</t>
-  </si>
-  <si>
-    <t>TaskDoCost</t>
-  </si>
-  <si>
-    <t>造成伤害</t>
-  </si>
-  <si>
-    <t>测试时间轴2</t>
-  </si>
-  <si>
-    <t>轨道1</t>
-  </si>
-  <si>
-    <t>调试3</t>
-  </si>
-  <si>
-    <t>开头</t>
-  </si>
-  <si>
-    <t>调试5</t>
-  </si>
-  <si>
-    <t>结尾</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务类型</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>通用参数：支持多态，添加新XParam类型去__bean__中添加即可。暂定给了10个变量的预留位，不够的话就自己加长。</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>1;25</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试新输出</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>CueLogging</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -285,6 +303,21 @@
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -320,46 +353,46 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="14">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -637,33 +670,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="16.21875" customWidth="1" style="3"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1" style="3"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1" style="3"/>
-    <col min="6" max="6" width="14.44140625" customWidth="1" style="3"/>
-    <col min="7" max="7" width="18.109375" customWidth="1" style="3"/>
-    <col min="8" max="8" width="14.44140625" customWidth="1" style="3"/>
-    <col min="9" max="9" width="16.77734375" customWidth="1" style="3"/>
-    <col min="10" max="10" width="15" customWidth="1" style="3"/>
+    <col min="3" max="3" width="16.21875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="18.109375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="14.44140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="16.77734375" style="3" customWidth="1"/>
+    <col min="10" max="10" width="15" style="3" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" customWidth="1"/>
+    <col min="12" max="12" width="14.88671875" customWidth="1"/>
+    <col min="13" max="13" width="13.6640625" customWidth="1"/>
+    <col min="14" max="14" width="11.88671875" customWidth="1"/>
+    <col min="15" max="15" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="12" t="s">
@@ -673,20 +711,20 @@
       <c r="H1" s="12"/>
       <c r="I1" s="12"/>
       <c r="J1" s="12"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
-      <c r="V1" s="9"/>
-    </row>
-    <row r="2">
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="7"/>
+      <c r="V1" s="8"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -709,20 +747,20 @@
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
       <c r="J2" s="12"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="8"/>
-      <c r="T2" s="8"/>
-      <c r="U2" s="8"/>
-      <c r="V2" s="9"/>
-    </row>
-    <row r="3" s="3" customFormat="1">
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="V2" s="8"/>
+    </row>
+    <row r="3" spans="1:26" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -730,7 +768,7 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="10" t="s">
         <v>2</v>
       </c>
       <c r="G3" s="12" t="s">
@@ -739,22 +777,22 @@
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
       <c r="J3" s="12"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="10"/>
-      <c r="V3" s="10"/>
-      <c r="W3" s="10"/>
-      <c r="X3" s="9"/>
-    </row>
-    <row r="4" s="3" customFormat="1">
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="8"/>
+    </row>
+    <row r="4" spans="1:26" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>0</v>
       </c>
@@ -762,35 +800,35 @@
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
-      <c r="S4" s="13"/>
-      <c r="T4" s="13"/>
-      <c r="U4" s="8"/>
-      <c r="V4" s="8"/>
-      <c r="W4" s="8"/>
-      <c r="X4" s="8"/>
-      <c r="Y4" s="9"/>
-    </row>
-    <row r="5">
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="11"/>
+      <c r="T4" s="11"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="8"/>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -809,40 +847,42 @@
       <c r="F5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="13"/>
-      <c r="T5" s="13"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="7"/>
-    </row>
-    <row r="6">
+        <v>46</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="6"/>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B6" s="2">
         <v>101</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" s="3">
         <v>30</v>
@@ -851,7 +891,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G6" s="3">
         <v>3</v>
@@ -860,18 +900,32 @@
         <v>25</v>
       </c>
       <c r="I6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="O6" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="R6" s="2"/>
+      <c r="Z6" s="3"/>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="F7" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="F7" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="G7" s="3">
         <v>6</v>
@@ -880,18 +934,19 @@
         <v>6</v>
       </c>
       <c r="I7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z7" s="3"/>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="F8" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="F8" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="G8" s="3">
         <v>3</v>
@@ -900,15 +955,16 @@
         <v>24</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>33</v>
+      </c>
+      <c r="Z8" s="3"/>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="F9" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G9" s="3">
         <v>1</v>
@@ -917,13 +973,14 @@
         <v>1</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>36</v>
+      </c>
+      <c r="Z9" s="3"/>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="G10" s="3">
         <v>9</v>
       </c>
@@ -931,18 +988,19 @@
         <v>9</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>36</v>
+      </c>
+      <c r="Z10" s="3"/>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B11" s="2">
         <v>102</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D11" s="3">
         <v>50</v>
@@ -951,7 +1009,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G11" s="3">
         <v>3</v>
@@ -960,16 +1018,17 @@
         <v>4</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>41</v>
+      </c>
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="G12" s="3">
         <v>15</v>
       </c>
@@ -977,27 +1036,27 @@
         <v>50</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="Z12" s="3"/>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="5">
     <mergeCell ref="J4:T4"/>
-    <mergeCell ref="J5:T5"/>
     <mergeCell ref="G3:J3"/>
     <mergeCell ref="F2:J2"/>
     <mergeCell ref="F1:J1"/>
+    <mergeCell ref="K5:X5"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="152511" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -64,15 +64,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t>##var</t>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>I</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -82,7 +82,7 @@
       </rPr>
       <t>D</t>
     </r>
-    <phoneticPr fontId="0" type="noConversion"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>Name</t>
@@ -94,10 +94,10 @@
     <t>ManualEndAbility</t>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>*</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -107,7 +107,7 @@
       </rPr>
       <t>T</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -117,7 +117,7 @@
       </rPr>
       <t>racks</t>
     </r>
-    <phoneticPr fontId="0" type="noConversion"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>##type</t>
@@ -132,10 +132,10 @@
     <t>bool</t>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>array,</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -145,7 +145,7 @@
       </rPr>
       <t>T</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -155,7 +155,7 @@
       </rPr>
       <t>rack</t>
     </r>
-    <phoneticPr fontId="0" type="noConversion"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>*TaskClips</t>
@@ -197,6 +197,12 @@
     <t>任务名（编辑时展示用）</t>
   </si>
   <si>
+    <t>任务类型</t>
+  </si>
+  <si>
+    <t>通用参数：支持多态，添加新XParam类型去__bean__中添加即可。暂定给了10个变量的预留位，不够的话就自己加长。</t>
+  </si>
+  <si>
     <t>普通攻击</t>
   </si>
   <si>
@@ -206,6 +212,21 @@
     <t>播放攻击动画</t>
   </si>
   <si>
+    <t>TaskPlayCue</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>CuePlayAnimator</t>
+  </si>
+  <si>
+    <t>root/animator</t>
+  </si>
+  <si>
+    <t>attack</t>
+  </si>
+  <si>
     <t>音效轨道</t>
   </si>
   <si>
@@ -255,41 +276,14 @@
   </si>
   <si>
     <t>结尾</t>
-  </si>
-  <si>
-    <t>TaskPlayCue</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>0;0</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>任务类型</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>通用参数：支持多态，添加新XParam类型去__bean__中添加即可。暂定给了10个变量的预留位，不够的话就自己加长。</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>1;25</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试新输出</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>CueLogging</t>
-    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -303,21 +297,6 @@
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -352,47 +331,48 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+  <cellXfs count="15">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -670,61 +650,61 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:Y12"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="16.21875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="14.44140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="18.109375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="14.44140625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="16.77734375" style="3" customWidth="1"/>
-    <col min="10" max="10" width="15" style="3" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" customWidth="1"/>
-    <col min="12" max="12" width="14.88671875" customWidth="1"/>
-    <col min="13" max="13" width="13.6640625" customWidth="1"/>
-    <col min="14" max="14" width="11.88671875" customWidth="1"/>
-    <col min="15" max="15" width="14.77734375" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" customWidth="1" style="4"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1" style="4"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1" style="4"/>
+    <col min="6" max="6" width="14.44140625" customWidth="1" style="4"/>
+    <col min="7" max="7" width="18.109375" customWidth="1" style="4"/>
+    <col min="8" max="8" width="14.44140625" customWidth="1" style="4"/>
+    <col min="9" max="9" width="16.77734375" customWidth="1" style="4"/>
+    <col min="10" max="10" width="15" customWidth="1" style="4"/>
+    <col min="11" max="11" width="12.33203125" customWidth="1" style="3"/>
+    <col min="12" max="12" width="14.88671875" customWidth="1" style="3"/>
+    <col min="13" max="13" width="13.6640625" customWidth="1" style="3"/>
+    <col min="14" max="14" width="11.88671875" customWidth="1" style="3"/>
+    <col min="15" max="15" width="14.77734375" customWidth="1" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="8"/>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="8"/>
+      <c r="V1" s="9"/>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -734,101 +714,101 @@
       <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="8"/>
-    </row>
-    <row r="3" spans="1:26" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
+      <c r="T2" s="8"/>
+      <c r="U2" s="8"/>
+      <c r="V2" s="9"/>
+    </row>
+    <row r="3" s="4" customFormat="1">
+      <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="10" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
-      <c r="V3" s="9"/>
-      <c r="W3" s="9"/>
-      <c r="X3" s="8"/>
-    </row>
-    <row r="4" spans="1:26" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="9"/>
+    </row>
+    <row r="4" s="4" customFormat="1">
+      <c r="A4" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="G4" s="10" t="s">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="G4" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
-      <c r="S4" s="11"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="8"/>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="12"/>
+      <c r="R4" s="12"/>
+      <c r="S4" s="12"/>
+      <c r="T4" s="12"/>
+      <c r="U4" s="8"/>
+      <c r="V4" s="8"/>
+      <c r="W4" s="8"/>
+      <c r="X4" s="8"/>
+      <c r="Y4" s="9"/>
+    </row>
+    <row r="5">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -838,216 +818,208 @@
       <c r="C5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="K5" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="11"/>
-      <c r="S5" s="11"/>
-      <c r="T5" s="11"/>
-      <c r="U5" s="11"/>
-      <c r="V5" s="11"/>
-      <c r="W5" s="11"/>
-      <c r="X5" s="11"/>
-      <c r="Y5" s="6"/>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="J5" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="12"/>
+      <c r="S5" s="12"/>
+      <c r="T5" s="12"/>
+      <c r="U5" s="12"/>
+      <c r="V5" s="12"/>
+      <c r="W5" s="12"/>
+      <c r="X5" s="12"/>
+      <c r="Y5" s="7"/>
+    </row>
+    <row r="6">
       <c r="B6" s="2">
         <v>101</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="4">
+        <v>30</v>
+      </c>
+      <c r="E6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="4">
+        <v>2</v>
+      </c>
+      <c r="H6" s="4">
         <v>24</v>
       </c>
-      <c r="D6" s="3">
+      <c r="I6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="3">
+      <c r="L6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="F7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="4">
+        <v>6</v>
+      </c>
+      <c r="H7" s="4">
+        <v>6</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="F8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="4">
         <v>3</v>
       </c>
-      <c r="H6" s="3">
-        <v>25</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" s="3" t="s">
+      <c r="H8" s="4">
+        <v>24</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="F9" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="4">
+        <v>1</v>
+      </c>
+      <c r="H9" s="4">
+        <v>1</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="G10" s="4">
+        <v>9</v>
+      </c>
+      <c r="H10" s="4">
+        <v>9</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="K6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="O6" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="R6" s="2"/>
-      <c r="Z6" s="3"/>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="F7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="3">
-        <v>6</v>
-      </c>
-      <c r="H7" s="3">
-        <v>6</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z7" s="3"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="F8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="3">
-        <v>3</v>
-      </c>
-      <c r="H8" s="3">
-        <v>24</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z8" s="3"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="F9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1</v>
-      </c>
-      <c r="H9" s="3">
-        <v>1</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z9" s="3"/>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="G10" s="3">
-        <v>9</v>
-      </c>
-      <c r="H10" s="3">
-        <v>9</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z10" s="3"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="J10" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="B11" s="2">
         <v>102</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="3">
+      <c r="C11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="4">
         <v>50</v>
       </c>
-      <c r="E11" s="3" t="b">
+      <c r="E11" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G11" s="3">
+      <c r="F11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="4">
         <v>3</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="4">
         <v>4</v>
       </c>
-      <c r="I11" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="G12" s="3">
+      <c r="I11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="G12" s="4">
         <v>15</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="4">
         <v>50</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z12" s="3"/>
+      <c r="I12" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells>
     <mergeCell ref="J4:T4"/>
     <mergeCell ref="G3:J3"/>
     <mergeCell ref="F2:J2"/>
@@ -1057,6 +1029,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
@@ -224,7 +224,7 @@
     <t>root/animator</t>
   </si>
   <si>
-    <t>attack</t>
+    <t>atk</t>
   </si>
   <si>
     <t>音效轨道</t>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46AB0371-B164-4F0E-9E69-3FFF08E9C42D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC128A6-4778-4338-904C-A57CA57E525C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511" fullCalcOnLoad="1"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -64,15 +64,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="50">
   <si>
     <t>##var</t>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <t>I</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -82,7 +82,7 @@
       </rPr>
       <t>D</t>
     </r>
-    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>Name</t>
@@ -94,10 +94,10 @@
     <t>ManualEndAbility</t>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <t>*</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -107,7 +107,7 @@
       </rPr>
       <t>T</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -117,7 +117,7 @@
       </rPr>
       <t>racks</t>
     </r>
-    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>##type</t>
@@ -132,10 +132,10 @@
     <t>bool</t>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <t>array,</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -145,7 +145,7 @@
       </rPr>
       <t>T</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -155,7 +155,7 @@
       </rPr>
       <t>rack</t>
     </r>
-    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>*TaskClips</t>
@@ -221,10 +221,7 @@
     <t>CuePlayAnimator</t>
   </si>
   <si>
-    <t>root/animator</t>
-  </si>
-  <si>
-    <t>atk</t>
+    <t>attack</t>
   </si>
   <si>
     <t>音效轨道</t>
@@ -282,8 +279,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -297,6 +293,21 @@
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -332,47 +343,47 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="15">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -653,22 +664,22 @@
   <dimension ref="A1:Y12"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="16.21875" customWidth="1" style="4"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1" style="4"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1" style="4"/>
-    <col min="6" max="6" width="14.44140625" customWidth="1" style="4"/>
-    <col min="7" max="7" width="18.109375" customWidth="1" style="4"/>
-    <col min="8" max="8" width="14.44140625" customWidth="1" style="4"/>
-    <col min="9" max="9" width="16.77734375" customWidth="1" style="4"/>
-    <col min="10" max="10" width="15" customWidth="1" style="4"/>
-    <col min="11" max="11" width="12.33203125" customWidth="1" style="3"/>
-    <col min="12" max="12" width="14.88671875" customWidth="1" style="3"/>
-    <col min="13" max="13" width="13.6640625" customWidth="1" style="3"/>
-    <col min="14" max="14" width="11.88671875" customWidth="1" style="3"/>
-    <col min="15" max="15" width="14.77734375" customWidth="1" style="3"/>
+    <col min="3" max="3" width="16.21875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="18.109375" style="4" customWidth="1"/>
+    <col min="8" max="8" width="14.44140625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="16.77734375" style="4" customWidth="1"/>
+    <col min="10" max="10" width="15" style="4" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="14.88671875" style="3" customWidth="1"/>
+    <col min="13" max="13" width="13.6640625" style="3" customWidth="1"/>
+    <col min="14" max="14" width="11.88671875" style="3" customWidth="1"/>
+    <col min="15" max="15" width="14.77734375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -684,13 +695,13 @@
       <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
       <c r="M1" s="8"/>
@@ -704,7 +715,7 @@
       <c r="U1" s="8"/>
       <c r="V1" s="9"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -720,13 +731,13 @@
       <c r="E2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
       <c r="M2" s="8"/>
@@ -740,7 +751,7 @@
       <c r="U2" s="8"/>
       <c r="V2" s="9"/>
     </row>
-    <row r="3" s="4" customFormat="1">
+    <row r="3" spans="1:25" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
@@ -751,12 +762,12 @@
       <c r="F3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
       <c r="K3" s="10"/>
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
@@ -772,7 +783,7 @@
       <c r="W3" s="10"/>
       <c r="X3" s="9"/>
     </row>
-    <row r="4" s="4" customFormat="1">
+    <row r="4" spans="1:25" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>0</v>
       </c>
@@ -789,26 +800,26 @@
       <c r="I4" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12"/>
-      <c r="S4" s="12"/>
-      <c r="T4" s="12"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="13"/>
+      <c r="T4" s="13"/>
       <c r="U4" s="8"/>
       <c r="V4" s="8"/>
       <c r="W4" s="8"/>
       <c r="X4" s="8"/>
       <c r="Y4" s="9"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -836,28 +847,28 @@
       <c r="I5" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="J5" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K5" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="12"/>
-      <c r="U5" s="12"/>
-      <c r="V5" s="12"/>
-      <c r="W5" s="12"/>
-      <c r="X5" s="12"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="13"/>
+      <c r="U5" s="13"/>
+      <c r="V5" s="13"/>
+      <c r="W5" s="13"/>
+      <c r="X5" s="13"/>
       <c r="Y5" s="7"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B6" s="2">
         <v>101</v>
       </c>
@@ -895,15 +906,15 @@
         <v>31</v>
       </c>
       <c r="N6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="O6" s="3" t="s">
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="F7" s="4" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="F7" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="G7" s="4">
         <v>6</v>
@@ -912,18 +923,18 @@
         <v>6</v>
       </c>
       <c r="I7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="K7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="K7" s="3" t="s">
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="F8" s="4" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="F8" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="G8" s="4">
         <v>3</v>
@@ -932,15 +943,15 @@
         <v>24</v>
       </c>
       <c r="I8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="J8" s="4" t="s">
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="F9" s="4" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="F9" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="G9" s="4">
         <v>1</v>
@@ -949,13 +960,13 @@
         <v>1</v>
       </c>
       <c r="I9" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J9" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J9" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10">
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="G10" s="4">
         <v>9</v>
       </c>
@@ -963,18 +974,18 @@
         <v>9</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B11" s="2">
         <v>102</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D11" s="4">
         <v>50</v>
@@ -983,7 +994,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G11" s="4">
         <v>3</v>
@@ -992,16 +1003,16 @@
         <v>4</v>
       </c>
       <c r="I11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="J11" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12">
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="G12" s="4">
         <v>15</v>
       </c>
@@ -1009,17 +1020,17 @@
         <v>50</v>
       </c>
       <c r="I12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="J12" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>50</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="5">
     <mergeCell ref="J4:T4"/>
     <mergeCell ref="G3:J3"/>
     <mergeCell ref="F2:J2"/>
@@ -1029,7 +1040,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC128A6-4778-4338-904C-A57CA57E525C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8775547E-C4AA-48A8-9FB1-973175D32583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="50">
   <si>
     <t>##var</t>
   </si>
@@ -167,112 +167,116 @@
     <t>EndTime</t>
   </si>
   <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>时间轴技能名字</t>
+  </si>
+  <si>
+    <t>技能生命时长</t>
+  </si>
+  <si>
+    <t>需要手动结束技能</t>
+  </si>
+  <si>
+    <t>轨道名</t>
+  </si>
+  <si>
+    <t>开始帧</t>
+  </si>
+  <si>
+    <t>结束帧</t>
+  </si>
+  <si>
+    <t>任务名（编辑时展示用）</t>
+  </si>
+  <si>
+    <t>任务类型</t>
+  </si>
+  <si>
+    <t>通用参数：支持多态，添加新XParam类型去__bean__中添加即可。暂定给了10个变量的预留位，不够的话就自己加长。</t>
+  </si>
+  <si>
+    <t>普通攻击</t>
+  </si>
+  <si>
+    <t>动画轨道</t>
+  </si>
+  <si>
+    <t>播放攻击动画</t>
+  </si>
+  <si>
+    <t>attack</t>
+  </si>
+  <si>
+    <t>音效轨道</t>
+  </si>
+  <si>
+    <t>播放攻击音效</t>
+  </si>
+  <si>
+    <t>TaskDebug</t>
+  </si>
+  <si>
+    <t>测试135</t>
+  </si>
+  <si>
+    <t>特效轨道</t>
+  </si>
+  <si>
+    <t>添加拖尾特效</t>
+  </si>
+  <si>
+    <t>TaskDoNothing</t>
+  </si>
+  <si>
+    <t>GE轨道</t>
+  </si>
+  <si>
+    <t>消耗</t>
+  </si>
+  <si>
+    <t>TaskDoCost</t>
+  </si>
+  <si>
+    <t>造成伤害</t>
+  </si>
+  <si>
+    <t>测试时间轴2</t>
+  </si>
+  <si>
+    <t>轨道1</t>
+  </si>
+  <si>
+    <t>调试3</t>
+  </si>
+  <si>
+    <t>开头</t>
+  </si>
+  <si>
+    <t>调试5</t>
+  </si>
+  <si>
+    <t>结尾</t>
+  </si>
+  <si>
     <t>Task</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>时间轴技能名字</t>
-  </si>
-  <si>
-    <t>技能生命时长</t>
-  </si>
-  <si>
-    <t>需要手动结束技能</t>
-  </si>
-  <si>
-    <t>轨道名</t>
-  </si>
-  <si>
-    <t>开始帧</t>
-  </si>
-  <si>
-    <t>结束帧</t>
-  </si>
-  <si>
-    <t>任务名（编辑时展示用）</t>
-  </si>
-  <si>
-    <t>任务类型</t>
-  </si>
-  <si>
-    <t>通用参数：支持多态，添加新XParam类型去__bean__中添加即可。暂定给了10个变量的预留位，不够的话就自己加长。</t>
-  </si>
-  <si>
-    <t>普通攻击</t>
-  </si>
-  <si>
-    <t>动画轨道</t>
-  </si>
-  <si>
-    <t>播放攻击动画</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>TaskPlayCue</t>
-  </si>
-  <si>
-    <t/>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>CuePlayAnimator</t>
-  </si>
-  <si>
-    <t>attack</t>
-  </si>
-  <si>
-    <t>音效轨道</t>
-  </si>
-  <si>
-    <t>播放攻击音效</t>
-  </si>
-  <si>
-    <t>TaskDebug</t>
-  </si>
-  <si>
-    <t>测试135</t>
-  </si>
-  <si>
-    <t>特效轨道</t>
-  </si>
-  <si>
-    <t>添加拖尾特效</t>
-  </si>
-  <si>
-    <t>TaskDoNothing</t>
-  </si>
-  <si>
-    <t>GE轨道</t>
-  </si>
-  <si>
-    <t>消耗</t>
-  </si>
-  <si>
-    <t>TaskDoCost</t>
-  </si>
-  <si>
-    <t>造成伤害</t>
-  </si>
-  <si>
-    <t>测试时间轴2</t>
-  </si>
-  <si>
-    <t>轨道1</t>
-  </si>
-  <si>
-    <t>调试3</t>
-  </si>
-  <si>
-    <t>开头</t>
-  </si>
-  <si>
-    <t>调试5</t>
-  </si>
-  <si>
-    <t>结尾</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>""</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -801,7 +805,7 @@
         <v>2</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="K4" s="13"/>
       <c r="L4" s="13"/>
@@ -821,37 +825,37 @@
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="H5" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="I5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="J5" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="K5" s="13" t="s">
         <v>24</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>25</v>
       </c>
       <c r="L5" s="13"/>
       <c r="M5" s="13"/>
@@ -873,7 +877,7 @@
         <v>101</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" s="4">
         <v>30</v>
@@ -882,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G6" s="4">
         <v>2</v>
@@ -891,30 +895,30 @@
         <v>24</v>
       </c>
       <c r="I6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K6" s="4">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="O6" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F7" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G7" s="4">
         <v>6</v>
@@ -923,18 +927,18 @@
         <v>6</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F8" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G8" s="4">
         <v>3</v>
@@ -943,15 +947,15 @@
         <v>24</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F9" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G9" s="4">
         <v>1</v>
@@ -960,10 +964,10 @@
         <v>1</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
@@ -974,10 +978,10 @@
         <v>9</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
@@ -985,7 +989,7 @@
         <v>102</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D11" s="4">
         <v>50</v>
@@ -994,7 +998,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G11" s="4">
         <v>3</v>
@@ -1003,13 +1007,13 @@
         <v>4</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
@@ -1020,13 +1024,13 @@
         <v>50</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="152511" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -64,15 +64,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>##var</t>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>I</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -82,7 +82,7 @@
       </rPr>
       <t>D</t>
     </r>
-    <phoneticPr fontId="0" type="noConversion"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>Name</t>
@@ -94,10 +94,10 @@
     <t>ManualEndAbility</t>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>*</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -107,7 +107,7 @@
       </rPr>
       <t>T</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -117,7 +117,7 @@
       </rPr>
       <t>racks</t>
     </r>
-    <phoneticPr fontId="0" type="noConversion"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>##type</t>
@@ -132,10 +132,10 @@
     <t>bool</t>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>array,</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -145,7 +145,7 @@
       </rPr>
       <t>T</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -155,7 +155,7 @@
       </rPr>
       <t>rack</t>
     </r>
-    <phoneticPr fontId="0" type="noConversion"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>*TaskClips</t>
@@ -167,6 +167,9 @@
     <t>EndTime</t>
   </si>
   <si>
+    <t>Task</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -209,6 +212,21 @@
     <t>播放攻击动画</t>
   </si>
   <si>
+    <t>TaskPlayCue</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>CuePlayAnimator</t>
+  </si>
+  <si>
+    <t>""</t>
+  </si>
+  <si>
     <t>attack</t>
   </si>
   <si>
@@ -261,29 +279,14 @@
   </si>
   <si>
     <t>结尾</t>
-  </si>
-  <si>
-    <t>Task</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>TaskPlayCue</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>CuePlayAnimator</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>""</t>
-    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -297,21 +300,6 @@
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -347,47 +335,47 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="15">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -668,22 +656,22 @@
   <dimension ref="A1:Y12"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="16.21875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="14.44140625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="18.109375" style="4" customWidth="1"/>
-    <col min="8" max="8" width="14.44140625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16.77734375" style="4" customWidth="1"/>
-    <col min="10" max="10" width="15" style="4" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" style="3" customWidth="1"/>
-    <col min="12" max="12" width="14.88671875" style="3" customWidth="1"/>
-    <col min="13" max="13" width="13.6640625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="11.88671875" style="3" customWidth="1"/>
-    <col min="15" max="15" width="14.77734375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" customWidth="1" style="4"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1" style="4"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1" style="4"/>
+    <col min="6" max="6" width="14.44140625" customWidth="1" style="4"/>
+    <col min="7" max="7" width="18.109375" customWidth="1" style="4"/>
+    <col min="8" max="8" width="14.44140625" customWidth="1" style="4"/>
+    <col min="9" max="9" width="16.77734375" customWidth="1" style="4"/>
+    <col min="10" max="10" width="15" customWidth="1" style="4"/>
+    <col min="11" max="11" width="12.33203125" customWidth="1" style="3"/>
+    <col min="12" max="12" width="14.88671875" customWidth="1" style="3"/>
+    <col min="13" max="13" width="13.6640625" customWidth="1" style="3"/>
+    <col min="14" max="14" width="11.88671875" customWidth="1" style="3"/>
+    <col min="15" max="15" width="14.77734375" customWidth="1" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -719,7 +707,7 @@
       <c r="U1" s="8"/>
       <c r="V1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -755,7 +743,7 @@
       <c r="U2" s="8"/>
       <c r="V2" s="9"/>
     </row>
-    <row r="3" spans="1:25" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" s="4" customFormat="1">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
@@ -787,7 +775,7 @@
       <c r="W3" s="10"/>
       <c r="X3" s="9"/>
     </row>
-    <row r="4" spans="1:25" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" s="4" customFormat="1">
       <c r="A4" s="6" t="s">
         <v>0</v>
       </c>
@@ -805,7 +793,7 @@
         <v>2</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="K4" s="13"/>
       <c r="L4" s="13"/>
@@ -823,39 +811,39 @@
       <c r="X4" s="8"/>
       <c r="Y4" s="9"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K5" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L5" s="13"/>
       <c r="M5" s="13"/>
@@ -872,12 +860,12 @@
       <c r="X5" s="13"/>
       <c r="Y5" s="7"/>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="B6" s="2">
         <v>101</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="4">
         <v>30</v>
@@ -886,7 +874,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G6" s="4">
         <v>2</v>
@@ -895,30 +883,30 @@
         <v>24</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="K6" s="4">
-        <v>0</v>
-      </c>
-      <c r="L6" s="4">
-        <v>0</v>
+        <v>29</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>49</v>
+        <v>32</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="F7" s="4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G7" s="4">
         <v>6</v>
@@ -927,18 +915,18 @@
         <v>6</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="F8" s="4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G8" s="4">
         <v>3</v>
@@ -947,15 +935,15 @@
         <v>24</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="F9" s="4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G9" s="4">
         <v>1</v>
@@ -964,13 +952,13 @@
         <v>1</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="G10" s="4">
         <v>9</v>
       </c>
@@ -978,18 +966,18 @@
         <v>9</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="B11" s="2">
         <v>102</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D11" s="4">
         <v>50</v>
@@ -998,7 +986,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G11" s="4">
         <v>3</v>
@@ -1007,16 +995,16 @@
         <v>4</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="G12" s="4">
         <v>15</v>
       </c>
@@ -1024,17 +1012,17 @@
         <v>50</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells>
     <mergeCell ref="J4:T4"/>
     <mergeCell ref="G3:J3"/>
     <mergeCell ref="F2:J2"/>
@@ -1044,6 +1032,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>